--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Slot Availability" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schedule Matrix'!$A$5:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schedule Matrix'!$A$5:$I$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I13"/>
+  <dimension ref="A2:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -748,7 +748,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Scheduled; currently private</t>
+          <t>Published publicly</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr"/>
@@ -848,8 +848,124 @@
       <c r="H13" s="6" t="inlineStr"/>
       <c r="I13" s="6" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Short 1: German Directions Vocabulary</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Short 2: Daily Routine Vocabulary</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Video 1: Asking for Directions in the City</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Video 2: Starting the Morning Routine</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:I13"/>
+  <autoFilter ref="A5:I17"/>
   <mergeCells count="2">
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A2:I2"/>
@@ -1021,7 +1137,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Short 1: German Directions Vocabulary</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1031,7 +1147,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Short 2: Daily Routine Vocabulary</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -1064,7 +1180,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 1: Asking for Directions in the City</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -1074,7 +1190,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 2: Starting the Morning Routine</t>
         </is>
       </c>
       <c r="G9" s="10">

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Slot Availability" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schedule Matrix'!$A$5:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schedule Matrix'!$A$5:$I$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I17"/>
+  <dimension ref="A2:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -854,12 +854,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Short 1: German Directions Vocabulary</t>
+          <t>Short 1: Grocery Shopping Vocabulary</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Short 2: Daily Routine Vocabulary</t>
+          <t>Short 2: Public Transport Vocabulary</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Video 1: Asking for Directions in the City</t>
+          <t>Video 1: Buying Fresh Fruit at the Grocery Store</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Video 2: Starting the Morning Routine</t>
+          <t>Video 2: Navigating the Train Station</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -964,8 +964,124 @@
       </c>
       <c r="I17" s="6" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Short 1: German Directions Vocabulary</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Short 2: Daily Routine Vocabulary</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Video 1: Asking for Directions in the City</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Video 2: Starting the Morning Routine</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:I17"/>
+  <autoFilter ref="A5:I21"/>
   <mergeCells count="2">
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A2:I2"/>
@@ -1175,7 +1291,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Short 1: Grocery Shopping Vocabulary</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1185,7 +1301,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Short 2: Public Transport Vocabulary</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -1218,7 +1334,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 1: Buying Fresh Fruit at the Grocery Store</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1228,7 +1344,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 2: Navigating the Train Station</t>
         </is>
       </c>
       <c r="G10" s="10">

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Short 2: Public Transport Vocabulary</t>
+          <t>Short 2: Next Train and Station Words</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Short 1: German Directions Vocabulary</t>
+          <t>Short 1: Street and Turn Words in German</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Video 1: Asking for Directions in the City</t>
+          <t>Video 1: Excuse Me, Where Is the Train Station?</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Short 1: German Directions Vocabulary</t>
+          <t>Short 1: Street and Turn Words in German</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Asking for Directions in the City</t>
+          <t>Video 1: Excuse Me, Where Is the Train Station?</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Short 2: Public Transport Vocabulary</t>
+          <t>Short 2: Next Train and Station Words</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Scheduled; currently private</t>
+          <t>Published publicly</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr"/>
@@ -1168,31 +1168,31 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 2: Asking for Directions in the City</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Short 1: German Public Transport Vocabulary</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 1: Buying a Train Ticket at the Station</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Short 2: German Direction Vocabulary</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="G6" s="10">
@@ -1206,16 +1206,16 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Video 2: Asking for Directions in the City</t>
+          <t>Short 1: Street and Turn Words in German</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Buying a Train Ticket at the Station</t>
+          <t>Short 2: Daily Routine Vocabulary</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1244,31 +1244,31 @@
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Short 1: Street and Turn Words in German</t>
+          <t>Short 1: Grocery Shopping Vocabulary</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 1: Excuse Me, Where Is the Train Station?</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Short 2: Daily Routine Vocabulary</t>
+          <t>Short 2: Next Train and Station Words</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 2: Starting the Morning Routine</t>
         </is>
       </c>
       <c r="G8" s="10">
@@ -1282,31 +1282,31 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Short 1: Grocery Shopping Vocabulary</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Excuse Me, Where Is the Train Station?</t>
+          <t>Video 1: Buying Fresh Fruit at the Grocery Store</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Short 2: Next Train and Station Words</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Video 2: Starting the Morning Routine</t>
+          <t>Video 2: Navigating the Train Station</t>
         </is>
       </c>
       <c r="G9" s="10">
@@ -1320,11 +1320,11 @@
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Buying Fresh Fruit at the Grocery Store</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Video 2: Navigating the Train Station</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="G10" s="10">
@@ -1358,11 +1358,11 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1396,11 +1396,11 @@
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -1434,11 +1434,11 @@
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1472,11 +1472,11 @@
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>46330</v>
+        <v>46331</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1510,11 +1510,11 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>46331</v>
+        <v>46332</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1548,11 +1548,11 @@
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1586,11 +1586,11 @@
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>46333</v>
+        <v>46334</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1624,11 +1624,11 @@
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>46334</v>
+        <v>46335</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1662,11 +1662,11 @@
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>46335</v>
+        <v>46336</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -835,7 +835,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Scheduled; currently private</t>
+          <t>Published publicly</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Slot Availability" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schedule Matrix'!$A$5:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schedule Matrix'!$A$5:$I$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I21"/>
+  <dimension ref="A2:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -806,7 +806,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Scheduled; currently private</t>
+          <t>Published publicly</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr"/>
@@ -1080,8 +1080,124 @@
       </c>
       <c r="I21" s="6" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Short 1: Office Desk Items and Actions in German</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Short 2: Classroom Materials and Study Tools in German</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Video 1: Printing an Office Document with a Colleague</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Video 2: Asking a Study Question in the Classroom</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:I21"/>
+  <autoFilter ref="A5:I25"/>
   <mergeCells count="2">
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A2:I2"/>
@@ -1291,7 +1407,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Short 1: Office Desk Items and Actions in German</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1301,7 +1417,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Short 2: Classroom Materials and Study Tools in German</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -1334,7 +1450,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 1: Printing an Office Document with a Colleague</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1344,7 +1460,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 2: Asking a Study Question in the Classroom</t>
         </is>
       </c>
       <c r="G10" s="10">

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -1284,16 +1284,16 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Video 2: Asking for Directions in the City</t>
+          <t>Short 1: Street and Turn Words in German</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Buying a Train Ticket at the Station</t>
+          <t>Short 2: Daily Routine Vocabulary</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -1322,31 +1322,31 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Short 1: Street and Turn Words in German</t>
+          <t>Short 1: Grocery Shopping Vocabulary</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 1: Excuse Me, Where Is the Train Station?</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Short 2: Daily Routine Vocabulary</t>
+          <t>Short 2: Next Train and Station Words</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 2: Starting the Morning Routine</t>
         </is>
       </c>
       <c r="G7" s="10">
@@ -1360,31 +1360,31 @@
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Short 1: Grocery Shopping Vocabulary</t>
+          <t>Short 1: Office Desk Items and Actions in German</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Excuse Me, Where Is the Train Station?</t>
+          <t>Video 1: Buying Fresh Fruit at the Grocery Store</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Short 2: Next Train and Station Words</t>
+          <t>Short 2: Classroom Materials and Study Tools in German</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Video 2: Starting the Morning Routine</t>
+          <t>Video 2: Navigating the Train Station</t>
         </is>
       </c>
       <c r="G8" s="10">
@@ -1398,31 +1398,31 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Short 1: Office Desk Items and Actions in German</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Buying Fresh Fruit at the Grocery Store</t>
+          <t>Video 1: Printing an Office Document with a Colleague</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Short 2: Classroom Materials and Study Tools in German</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Video 2: Navigating the Train Station</t>
+          <t>Video 2: Asking a Study Question in the Classroom</t>
         </is>
       </c>
       <c r="G9" s="10">
@@ -1436,11 +1436,11 @@
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Printing an Office Document with a Colleague</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Video 2: Asking a Study Question in the Classroom</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="G10" s="10">
@@ -1474,11 +1474,11 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1512,11 +1512,11 @@
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -1550,11 +1550,11 @@
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>46330</v>
+        <v>46331</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1588,11 +1588,11 @@
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>46331</v>
+        <v>46332</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1626,11 +1626,11 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1664,11 +1664,11 @@
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>46333</v>
+        <v>46334</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1702,11 +1702,11 @@
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>46334</v>
+        <v>46335</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1740,11 +1740,11 @@
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>46335</v>
+        <v>46336</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1778,11 +1778,11 @@
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>46336</v>
+        <v>46337</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Scheduled; currently private</t>
+          <t>Published publicly</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Slot Availability" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schedule Matrix'!$A$5:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schedule Matrix'!$A$5:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I25"/>
+  <dimension ref="A2:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1196,8 +1196,124 @@
       </c>
       <c r="I25" s="6" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Short 1: Essential Weather and Outfit Words in German</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Short 2: Useful Bakery and Pastry Terms in German</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Video 1: Checking the Outdoor Weather and Choosing a Jacket</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Video 2: Stopping by the Local Bakery for Morning Treats</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled; currently private</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:I25"/>
+  <autoFilter ref="A5:I29"/>
   <mergeCells count="2">
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A2:I2"/>
@@ -1407,7 +1523,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Short 1: Essential Weather and Outfit Words in German</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1417,7 +1533,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Short 2: Useful Bakery and Pastry Terms in German</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -1450,7 +1566,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 1: Checking the Outdoor Weather and Choosing a Jacket</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1460,7 +1576,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 2: Stopping by the Local Bakery for Morning Treats</t>
         </is>
       </c>
       <c r="G10" s="10">

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -1009,7 +1009,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Scheduled; currently private</t>
+          <t>Published publicly</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr"/>

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -1400,31 +1400,31 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Short 1: Street and Turn Words in German</t>
+          <t>Short 1: Grocery Shopping Vocabulary</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 1: Excuse Me, Where Is the Train Station?</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Short 2: Daily Routine Vocabulary</t>
+          <t>Short 2: Next Train and Station Words</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Video 2: Starting the Morning Routine</t>
         </is>
       </c>
       <c r="G6" s="10">
@@ -1438,31 +1438,31 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Short 1: Grocery Shopping Vocabulary</t>
+          <t>Short 1: Office Desk Items and Actions in German</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Excuse Me, Where Is the Train Station?</t>
+          <t>Video 1: Buying Fresh Fruit at the Grocery Store</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Short 2: Next Train and Station Words</t>
+          <t>Short 2: Classroom Materials and Study Tools in German</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Video 2: Starting the Morning Routine</t>
+          <t>Video 2: Navigating the Train Station</t>
         </is>
       </c>
       <c r="G7" s="10">
@@ -1476,31 +1476,31 @@
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Short 1: Office Desk Items and Actions in German</t>
+          <t>Short 1: Essential Weather and Outfit Words in German</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Buying Fresh Fruit at the Grocery Store</t>
+          <t>Video 1: Printing an Office Document with a Colleague</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Short 2: Classroom Materials and Study Tools in German</t>
+          <t>Short 2: Useful Bakery and Pastry Terms in German</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Video 2: Navigating the Train Station</t>
+          <t>Video 2: Asking a Study Question in the Classroom</t>
         </is>
       </c>
       <c r="G8" s="10">
@@ -1514,31 +1514,31 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Short 1: Essential Weather and Outfit Words in German</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Printing an Office Document with a Colleague</t>
+          <t>Video 1: Checking the Outdoor Weather and Choosing a Jacket</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Short 2: Useful Bakery and Pastry Terms in German</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Video 2: Asking a Study Question in the Classroom</t>
+          <t>Video 2: Stopping by the Local Bakery for Morning Treats</t>
         </is>
       </c>
       <c r="G9" s="10">
@@ -1552,11 +1552,11 @@
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Checking the Outdoor Weather and Choosing a Jacket</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Video 2: Stopping by the Local Bakery for Morning Treats</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="G10" s="10">
@@ -1590,11 +1590,11 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1628,11 +1628,11 @@
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>46330</v>
+        <v>46331</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -1666,11 +1666,11 @@
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>46331</v>
+        <v>46332</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1704,11 +1704,11 @@
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1742,11 +1742,11 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>46333</v>
+        <v>46334</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1780,11 +1780,11 @@
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>46334</v>
+        <v>46335</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1818,11 +1818,11 @@
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>46335</v>
+        <v>46336</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1856,11 +1856,11 @@
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>46336</v>
+        <v>46337</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1894,11 +1894,11 @@
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>46337</v>
+        <v>46338</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -864,7 +864,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Scheduled; currently private</t>
+          <t>Published publicly</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Scheduled; currently private</t>
+          <t>Published publicly</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr"/>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Scheduled; currently private</t>
+          <t>Published publicly</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr"/>

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Scheduled; currently private</t>
+          <t>Published publicly</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
@@ -1400,31 +1400,31 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Short 1: Grocery Shopping Vocabulary</t>
+          <t>Short 1: Office Desk Items and Actions in German</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Excuse Me, Where Is the Train Station?</t>
+          <t>Video 1: Buying Fresh Fruit at the Grocery Store</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Short 2: Next Train and Station Words</t>
+          <t>Short 2: Classroom Materials and Study Tools in German</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Video 2: Starting the Morning Routine</t>
+          <t>Video 2: Navigating the Train Station</t>
         </is>
       </c>
       <c r="G6" s="10">
@@ -1438,31 +1438,31 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Short 1: Office Desk Items and Actions in German</t>
+          <t>Short 1: Essential Weather and Outfit Words in German</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Buying Fresh Fruit at the Grocery Store</t>
+          <t>Video 1: Printing an Office Document with a Colleague</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Short 2: Classroom Materials and Study Tools in German</t>
+          <t>Short 2: Useful Bakery and Pastry Terms in German</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Video 2: Navigating the Train Station</t>
+          <t>Video 2: Asking a Study Question in the Classroom</t>
         </is>
       </c>
       <c r="G7" s="10">
@@ -1476,31 +1476,31 @@
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Short 1: Essential Weather and Outfit Words in German</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Printing an Office Document with a Colleague</t>
+          <t>Video 1: Checking the Outdoor Weather and Choosing a Jacket</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Short 2: Useful Bakery and Pastry Terms in German</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Video 2: Asking a Study Question in the Classroom</t>
+          <t>Video 2: Stopping by the Local Bakery for Morning Treats</t>
         </is>
       </c>
       <c r="G8" s="10">
@@ -1514,11 +1514,11 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Video 1: Checking the Outdoor Weather and Choosing a Jacket</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Video 2: Stopping by the Local Bakery for Morning Treats</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="G9" s="10">
@@ -1552,11 +1552,11 @@
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1590,11 +1590,11 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>46330</v>
+        <v>46331</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1628,11 +1628,11 @@
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>46331</v>
+        <v>46332</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -1666,11 +1666,11 @@
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1704,11 +1704,11 @@
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>46333</v>
+        <v>46334</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1742,11 +1742,11 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>46334</v>
+        <v>46335</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1780,11 +1780,11 @@
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>46335</v>
+        <v>46336</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1818,11 +1818,11 @@
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>46336</v>
+        <v>46337</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1856,11 +1856,11 @@
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>46337</v>
+        <v>46338</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1894,11 +1894,11 @@
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>46338</v>
+        <v>46339</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -1096,7 +1096,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Scheduled; currently private</t>
+          <t>Published publicly</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -922,7 +922,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Scheduled; currently private</t>
+          <t>Published publicly</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr"/>

--- a/tracker/publishing_schedule.xlsx
+++ b/tracker/publishing_schedule.xlsx
@@ -1125,7 +1125,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Scheduled; currently private</t>
+          <t>Published publicly</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr"/>
